--- a/tmp/프로젝트 제출양식/2. 프로젝트 결과 보고서/20260428_개인 프로젝트 결과 보고서.xlsx
+++ b/tmp/프로젝트 제출양식/2. 프로젝트 결과 보고서/20260428_개인 프로젝트 결과 보고서.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20400" windowHeight="8970"/>
   </bookViews>
   <sheets>
-    <sheet name="개인 프로젝트 결과보고서" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="개인 프로젝트 결과보고서" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
@@ -22,6 +22,9 @@
     <t>프로젝트 제목</t>
   </si>
   <si>
+    <t>VARO Shopping Mall (바로 쇼핑몰)</t>
+  </si>
+  <si>
     <t>과정명</t>
   </si>
   <si>
@@ -37,95 +40,82 @@
     <t>발표일</t>
   </si>
   <si>
+    <t>2026. 04. 30</t>
+  </si>
+  <si>
     <t>담당강사</t>
   </si>
   <si>
+    <t>유 영 식</t>
+  </si>
+  <si>
     <t>컨셉</t>
   </si>
   <si>
+    <t>20~30 대 트렌디한 남성 패션 셀렉트 샵</t>
+  </si>
+  <si>
     <t>기능</t>
   </si>
   <si>
-    <t>- 실시간 데이터 동기화 (BroadcastChannel API)
+    <t xml:space="preserve">- 실시간 데이터 동기화 (BroadcastChannel API)
 - 커뮤니티 동적 페이징 (공지사항, 리뷰)
 - 어드민 Q&amp;A 통합 관리 대시보드 (통계 카드 및 실시간 필터)
-- 시스템구성도, ERD, UseCase, 요구사항정의서 정밀 자동 생성 (Excel/PNG)</t>
+- 시스템구성도, ERD, UseCase, 요구사항정의서 정밀 자동 생성 (Excel/PNG)
+- 쿠폰 고도화(프로모션 코드, 발급 수량 제어, 리뷰 작성자 타겟팅) 및 구매 금액별 자동 회원 등급 갱신 시스템 구축</t>
   </si>
   <si>
     <t>특장점</t>
   </si>
   <si>
-    <t>- LocalStorage Source of Truth 확보를 통한 도메인 간 데이터 정합성 보장
+    <t xml:space="preserve">- LocalStorage Source of Truth 확보를 통한 도메인 간 데이터 정합성 보장
 - AI 안티그래비티와의 협업을 통해 복잡한 시스템 아키텍처의 빠른 시각화 달성
 - 기업용 문서 표준에 부합하는 체계적인 개발 산출물 작성 표준화</t>
   </si>
   <si>
-    <t>사용기술 및
+    <t xml:space="preserve">사용기술 및
 개발환경</t>
   </si>
   <si>
-    <t>- 개발환경 : Windows 11
+    <t xml:space="preserve">- 개발환경 : Windows 11
 - 개발도구 : VS Code, Git, Google Chrome, AI 안티그래비티 (AI Coding Assistant)
 - 개발언어 및 프레임워크 : JavaScript(ES6+), Node.js, Express.js
 - DB : MySQL (InnoDB)
 - 라이브러리 및 API : ExcelJS, Mermaid, PlantUML</t>
-  </si>
-  <si>
-    <t>VARO Shopping Mall (바로 쇼핑몰)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>유 영 식</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026. 04. 30</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>20~30 대 트렌디한 남성 패션 셀렉트 샵</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <charset val="129"/>
+      <color theme="0"/>
+      <family val="3"/>
+      <sz val="20"/>
       <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="20"/>
-      <color theme="0"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <sz val="11"/>
       <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <charset val="129"/>
       <family val="3"/>
-      <charset val="129"/>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
     </font>
   </fonts>
   <fills count="4">
@@ -137,13 +127,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDEEAF6"/>
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="1"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFDEEAF6"/>
       </patternFill>
     </fill>
   </fills>
@@ -156,18 +146,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -176,24 +158,24 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -472,7 +454,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I11"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.625" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -482,149 +464,148 @@
     <col min="9" max="9" width="7.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="31.5">
-      <c r="B2" s="5" t="s">
+    <row r="2" ht="31.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-    </row>
-    <row r="4" spans="2:9">
-      <c r="B4" s="1" t="s">
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+    </row>
+    <row r="8" ht="36" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+    </row>
+    <row r="9" ht="120" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+    </row>
+    <row r="10" ht="108" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-    </row>
-    <row r="5" spans="2:9">
-      <c r="B5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-    </row>
-    <row r="6" spans="2:9">
-      <c r="B6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-    </row>
-    <row r="7" spans="2:9">
-      <c r="B7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="3" t="s">
+      <c r="C10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+    </row>
+    <row r="11" ht="110.1" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-    </row>
-    <row r="8" spans="2:9" ht="36" customHeight="1">
-      <c r="B8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="C11" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-    </row>
-    <row r="9" spans="2:9" ht="120" customHeight="1">
-      <c r="B9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-    </row>
-    <row r="10" spans="2:9" ht="108" customHeight="1">
-      <c r="B10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-    </row>
-    <row r="11" spans="2:9" ht="110.1" customHeight="1">
-      <c r="B11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="C8:I8"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="C10:I10"/>
-    <mergeCell ref="C11:I11"/>
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="C4:I4"/>
     <mergeCell ref="C5:I5"/>
     <mergeCell ref="C6:I6"/>
     <mergeCell ref="C7:E7"/>
     <mergeCell ref="G7:I7"/>
+    <mergeCell ref="C8:I8"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="C10:I10"/>
+    <mergeCell ref="C11:I11"/>
   </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/tmp/프로젝트 제출양식/2. 프로젝트 결과 보고서/20260428_개인 프로젝트 결과 보고서.xlsx
+++ b/tmp/프로젝트 제출양식/2. 프로젝트 결과 보고서/20260428_개인 프로젝트 결과 보고서.xlsx
@@ -81,7 +81,8 @@
 - 개발도구 : VS Code, Git, Google Chrome, AI 안티그래비티 (AI Coding Assistant)
 - 개발언어 및 프레임워크 : JavaScript(ES6+), Node.js, Express.js
 - DB : MySQL (InnoDB)
-- 라이브러리 및 API : ExcelJS, Mermaid, PlantUML</t>
+- 라이브러리 및 API : ExcelJS, Mermaid, PlantUML
+- 형상관리 및 배포 : Git, GitHub (main 브랜치 기반 실시간 배포 반영)</t>
   </si>
 </sst>
 </file>

--- a/tmp/프로젝트 제출양식/2. 프로젝트 결과 보고서/20260428_개인 프로젝트 결과 보고서.xlsx
+++ b/tmp/프로젝트 제출양식/2. 프로젝트 결과 보고서/20260428_개인 프로젝트 결과 보고서.xlsx
@@ -82,7 +82,9 @@
 - 개발언어 및 프레임워크 : JavaScript(ES6+), Node.js, Express.js
 - DB : MySQL (InnoDB)
 - 라이브러리 및 API : ExcelJS, Mermaid, PlantUML
-- 형상관리 및 배포 : Git, GitHub (main 브랜치 기반 실시간 배포 반영)</t>
+- 클라우드 DB : TiDB Cloud (MySQL 호환 분산 DB)
+- 서버 호스팅/배포 : Render
+- 형상관리 : Git, GitHub</t>
   </si>
 </sst>
 </file>

--- a/tmp/프로젝트 제출양식/2. 프로젝트 결과 보고서/20260428_개인 프로젝트 결과 보고서.xlsx
+++ b/tmp/프로젝트 제출양식/2. 프로젝트 결과 보고서/20260428_개인 프로젝트 결과 보고서.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20400" windowHeight="8970"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="개인 프로젝트 결과보고서" state="visible" r:id="rId4"/>
+    <sheet name="개인 프로젝트 결과보고서" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -52,13 +52,10 @@
     <t>컨셉</t>
   </si>
   <si>
-    <t>20~30 대 트렌디한 남성 패션 셀렉트 샵</t>
-  </si>
-  <si>
     <t>기능</t>
   </si>
   <si>
-    <t xml:space="preserve">- 실시간 데이터 동기화 (BroadcastChannel API)
+    <t>- 실시간 데이터 동기화 (BroadcastChannel API)
 - 커뮤니티 동적 페이징 (공지사항, 리뷰)
 - 어드민 Q&amp;A 통합 관리 대시보드 (통계 카드 및 실시간 필터)
 - 시스템구성도, ERD, UseCase, 요구사항정의서 정밀 자동 생성 (Excel/PNG)
@@ -68,16 +65,16 @@
     <t>특장점</t>
   </si>
   <si>
-    <t xml:space="preserve">- LocalStorage Source of Truth 확보를 통한 도메인 간 데이터 정합성 보장
+    <t>- LocalStorage Source of Truth 확보를 통한 도메인 간 데이터 정합성 보장
 - AI 안티그래비티와의 협업을 통해 복잡한 시스템 아키텍처의 빠른 시각화 달성
 - 기업용 문서 표준에 부합하는 체계적인 개발 산출물 작성 표준화</t>
   </si>
   <si>
-    <t xml:space="preserve">사용기술 및
+    <t>사용기술 및
 개발환경</t>
   </si>
   <si>
-    <t xml:space="preserve">- 개발환경 : Windows 11
+    <t>- 개발환경 : Windows 11
 - 개발도구 : VS Code, Git, Google Chrome, AI 안티그래비티 (AI Coding Assistant)
 - 개발언어 및 프레임워크 : JavaScript(ES6+), Node.js, Express.js
 - DB : MySQL (InnoDB)
@@ -86,39 +83,50 @@
 - 서버 호스팅/배포 : Render
 - 형상관리 : Git, GitHub</t>
   </si>
+  <si>
+    <t>20~30대 트렌디한 남성 패션 셀렉트 샵</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="20"/>
+      <color theme="0"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
-      <color theme="0"/>
-      <family val="3"/>
-      <sz val="20"/>
-      <name val="맑은 고딕"/>
     </font>
     <font>
       <b/>
-      <charset val="129"/>
-      <family val="3"/>
       <sz val="11"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
-      <charset val="129"/>
-      <family val="3"/>
       <sz val="11"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -149,10 +157,18 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -161,11 +177,11 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -178,7 +194,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -457,7 +473,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I11"/>
-  <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.625" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -467,20 +483,20 @@
     <col min="9" max="9" width="7.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="31.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="2:9" ht="31.5" customHeight="1">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B4" s="2" t="s">
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="4" spans="2:9">
+      <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
@@ -493,8 +509,8 @@
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B5" s="2" t="s">
+    <row r="5" spans="2:9">
+      <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
@@ -507,22 +523,22 @@
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B6" s="2" t="s">
+    <row r="6" spans="2:9">
+      <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B7" s="2" t="s">
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+    </row>
+    <row r="7" spans="2:9">
+      <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="4" t="s">
@@ -530,7 +546,7 @@
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G7" s="4" t="s">
@@ -539,12 +555,12 @@
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
     </row>
-    <row r="8" ht="36" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="2" t="s">
+    <row r="8" spans="2:9" ht="36" customHeight="1">
+      <c r="B8" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -553,12 +569,12 @@
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
     </row>
-    <row r="9" ht="120" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B9" s="2" t="s">
+    <row r="9" spans="2:9" ht="120" customHeight="1">
+      <c r="B9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>13</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>14</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
@@ -567,12 +583,12 @@
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
     </row>
-    <row r="10" ht="108" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B10" s="2" t="s">
+    <row r="10" spans="2:9" ht="108" customHeight="1">
+      <c r="B10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>15</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>16</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
@@ -581,12 +597,12 @@
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
     </row>
-    <row r="11" ht="110.1" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="2" t="s">
+    <row r="11" spans="2:9" ht="153" customHeight="1">
+      <c r="B11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>17</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>18</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
@@ -597,18 +613,19 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C8:I8"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="C10:I10"/>
+    <mergeCell ref="C11:I11"/>
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="C4:I4"/>
     <mergeCell ref="C5:I5"/>
     <mergeCell ref="C6:I6"/>
     <mergeCell ref="C7:E7"/>
     <mergeCell ref="G7:I7"/>
-    <mergeCell ref="C8:I8"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="C10:I10"/>
-    <mergeCell ref="C11:I11"/>
   </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
 </worksheet>
 </file>